--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -631,7 +631,7 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.58</v>
+        <v>57.59</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -671,25 +671,25 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N3" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -719,19 +719,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.58</v>
+        <v>52.59</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11|16|20|31|41|5</t>
+          <t>15|19|24|29|42|18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -762,25 +762,25 @@
         <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -813,16 +813,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.58</v>
+        <v>51.59</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1|13|18|34|37|5</t>
+          <t>11|16|20|31|41|5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -850,28 +850,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -889,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -901,19 +901,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.58</v>
+        <v>50.09</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2|9|19|31|34|2</t>
+          <t>16|19|22|29|43|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -941,28 +941,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -980,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -992,19 +992,19 @@
         <v>0.5</v>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>50.08</v>
+        <v>49.34</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15|20|24|29|39|11</t>
+          <t>1|12|13|28|37|18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1032,28 +1032,28 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1071,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1086,16 +1086,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>49.33</v>
+        <v>48.92333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|13</t>
+          <t>10|20|23|31|41|15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1126,22 +1126,22 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>19</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24</v>
+      </c>
+      <c r="K8" t="n">
+        <v>34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>37</v>
+      </c>
+      <c r="M8" t="n">
         <v>12</v>
-      </c>
-      <c r="I8" t="n">
-        <v>15</v>
-      </c>
-      <c r="J8" t="n">
-        <v>20</v>
-      </c>
-      <c r="K8" t="n">
-        <v>29</v>
-      </c>
-      <c r="L8" t="n">
-        <v>45</v>
-      </c>
-      <c r="M8" t="n">
-        <v>11</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1177,16 +1177,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.58</v>
+        <v>48.59</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12|15|20|29|45|11</t>
+          <t>7|19|24|34|37|12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
         <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
         <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1265,19 +1265,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>46.86571428571428</v>
+        <v>48.31727272727273</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11|19|24|28|31|3</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>45.91333333333333</v>
+        <v>47.59</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9|15|24|29|36|1</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.30727272727272</v>
+        <v>46.87571428571429</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9|19|24|34|35|18</t>
+          <t>13|15|20|29|30|2</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -580,25 +580,25 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L2" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N2" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -607,7 +607,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -628,19 +628,19 @@
         <v>0.5</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.59</v>
+        <v>60.57</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7|13|24|29|34|11</t>
+          <t>9|15|20|38|43|18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
     </row>
@@ -671,25 +671,25 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -719,19 +719,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>52.59</v>
+        <v>55.57</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15|19|24|29|42|18</t>
+          <t>2|22|23|31|43|17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
     </row>
@@ -759,28 +759,28 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" t="n">
+        <v>29</v>
+      </c>
+      <c r="L4" t="n">
+        <v>43</v>
+      </c>
+      <c r="M4" t="n">
         <v>11</v>
       </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K4" t="n">
-        <v>31</v>
-      </c>
-      <c r="L4" t="n">
-        <v>41</v>
-      </c>
-      <c r="M4" t="n">
-        <v>5</v>
-      </c>
       <c r="N4" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -810,19 +810,19 @@
         <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.59</v>
+        <v>50.07</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11|16|20|31|41|5</t>
+          <t>16|19|22|29|43|11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
     </row>
@@ -850,28 +850,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N5" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -889,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -901,19 +901,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.09</v>
+        <v>49.32</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16|19|22|29|43|11</t>
+          <t>10|20|23|31|41|15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
     </row>
@@ -941,28 +941,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -980,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -995,16 +995,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.34</v>
+        <v>48.90333333333333</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|12|13|28|37|18</t>
+          <t>9|19|20|30|43|3</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
     </row>
@@ -1032,28 +1032,28 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
         <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1071,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1083,19 +1083,19 @@
         <v>0.5</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.92333333333333</v>
+        <v>48.57</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10|20|23|31|41|15</t>
+          <t>15|20|24|29|39|11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
         <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1177,16 +1177,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.59</v>
+        <v>48.57</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|12</t>
+          <t>7|19|24|34|37|13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
     </row>
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22</v>
+      </c>
+      <c r="K9" t="n">
+        <v>29</v>
+      </c>
+      <c r="L9" t="n">
+        <v>35</v>
+      </c>
+      <c r="M9" t="n">
         <v>13</v>
       </c>
-      <c r="J9" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" t="n">
-        <v>28</v>
-      </c>
-      <c r="L9" t="n">
-        <v>39</v>
-      </c>
-      <c r="M9" t="n">
-        <v>18</v>
-      </c>
       <c r="N9" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1265,19 +1265,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>48.31727272727273</v>
+        <v>47.57</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11|13|20|28|39|18</t>
+          <t>8|9|22|29|35|13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
     </row>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
         <v>19</v>
@@ -1317,16 +1317,16 @@
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>47.59</v>
+        <v>46.85571428571428</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>14|19|24|29|35|5</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
     </row>
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
+        <v>11</v>
+      </c>
+      <c r="I11" t="n">
         <v>13</v>
-      </c>
-      <c r="I11" t="n">
-        <v>15</v>
       </c>
       <c r="J11" t="n">
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="N11" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>46.87571428571429</v>
+        <v>45.29727272727273</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13|15|20|29|30|2</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -580,25 +580,25 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
         <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M2" t="n">
         <v>18</v>
       </c>
       <c r="N2" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -631,16 +631,16 @@
         <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>60.57</v>
+        <v>60.55</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9|15|20|38|43|18</t>
+          <t>7|13|20|34|41|18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.57</v>
+        <v>55.55</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -762,13 +762,13 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
         <v>29</v>
@@ -777,10 +777,10 @@
         <v>43</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -810,19 +810,19 @@
         <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>50.07</v>
+        <v>53.05</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16|19|22|29|43|11</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -850,28 +850,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -889,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.125</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -904,16 +904,16 @@
         <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>49.32</v>
+        <v>50.55</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10|20|23|31|41|15</t>
+          <t>5|21|22|29|38|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
         <v>9</v>
@@ -980,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -995,7 +995,7 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>48.90333333333333</v>
+        <v>49.83571428571428</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1038,22 +1038,22 @@
         <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1086,16 +1086,16 @@
         <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.57</v>
+        <v>48.55</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15|20|24|29|39|11</t>
+          <t>15|22|25|31|36|5</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -1141,7 +1141,7 @@
         <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1162,7 +1162,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
@@ -1174,19 +1174,19 @@
         <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.57</v>
+        <v>46.3</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|13</t>
+          <t>7|19|24|34|37|16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
         <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1268,16 +1268,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>47.57</v>
+        <v>45.88333333333333</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8|9|22|29|35|13</t>
+          <t>9|15|24|29|36|1</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N10" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.85571428571428</v>
+        <v>45.55</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14|19|24|29|35|5</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1399,25 +1399,25 @@
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="M11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N11" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.29727272727273</v>
+        <v>45.27727272727272</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11|13|20|28|39|18</t>
+          <t>9|20|25|26|29|17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -586,19 +586,19 @@
         <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K2" t="n">
+        <v>29</v>
+      </c>
+      <c r="L2" t="n">
         <v>34</v>
       </c>
-      <c r="L2" t="n">
-        <v>41</v>
-      </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -607,7 +607,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -628,19 +628,19 @@
         <v>0.5</v>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>60.55</v>
+        <v>57.59</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7|13|20|34|41|18</t>
+          <t>7|13|24|29|34|11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -671,25 +671,25 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N3" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -719,19 +719,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.55</v>
+        <v>52.59</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2|22|23|31|43|17</t>
+          <t>15|19|24|29|42|18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -759,25 +759,25 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
         <v>119</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -813,16 +813,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>53.05</v>
+        <v>51.59</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|7</t>
+          <t>11|16|20|31|41|5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
         <v>22</v>
@@ -865,13 +865,13 @@
         <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -889,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -901,19 +901,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.55</v>
+        <v>50.09</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5|21|22|29|38|11</t>
+          <t>16|19|22|29|43|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -941,28 +941,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -980,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -995,16 +995,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.83571428571428</v>
+        <v>49.34</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9|19|20|30|43|3</t>
+          <t>1|12|13|28|37|18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1032,28 +1032,28 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
         <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1071,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1083,19 +1083,19 @@
         <v>0.5</v>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.55</v>
+        <v>48.92333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15|22|25|31|36|5</t>
+          <t>10|20|23|31|41|15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -1141,7 +1141,7 @@
         <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1162,7 +1162,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
@@ -1174,19 +1174,19 @@
         <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>46.3</v>
+        <v>48.59</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|16</t>
+          <t>7|19|24|34|37|12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1265,19 +1265,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>45.88333333333333</v>
+        <v>48.31727272727273</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9|15|24|29|36|1</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>45.55</v>
+        <v>47.59</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11|13|20|28|39|18</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" t="n">
         <v>20</v>
       </c>
-      <c r="J11" t="n">
-        <v>25</v>
-      </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.27727272727272</v>
+        <v>46.87571428571429</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9|20|25|26|29|17</t>
+          <t>13|15|20|29|30|2</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -631,7 +631,7 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.59</v>
+        <v>57.6</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -671,10 +671,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
         <v>15</v>
-      </c>
-      <c r="I3" t="n">
-        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
@@ -683,13 +683,13 @@
         <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -719,19 +719,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>52.59</v>
+        <v>55.6</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15|19|24|29|42|18</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -759,28 +759,28 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" t="n">
+        <v>29</v>
+      </c>
+      <c r="L4" t="n">
+        <v>38</v>
+      </c>
+      <c r="M4" t="n">
         <v>4</v>
       </c>
-      <c r="H4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K4" t="n">
-        <v>31</v>
-      </c>
-      <c r="L4" t="n">
-        <v>41</v>
-      </c>
-      <c r="M4" t="n">
-        <v>5</v>
-      </c>
       <c r="N4" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -813,16 +813,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.59</v>
+        <v>53.1</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11|16|20|31|41|5</t>
+          <t>3|21|22|29|38|4</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -850,28 +850,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -889,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -901,19 +901,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.09</v>
+        <v>49.88571428571429</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16|19|22|29|43|11</t>
+          <t>1|13|18|34|37|5</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -941,28 +941,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -980,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -995,16 +995,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.34</v>
+        <v>48.93333333333333</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|12|13|28|37|18</t>
+          <t>3|15|20|29|38|14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1032,28 +1032,28 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1071,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1083,19 +1083,19 @@
         <v>0.5</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.92333333333333</v>
+        <v>48.6</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10|20|23|31|41|15</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1126,22 +1126,22 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
         <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L8" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1177,16 +1177,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.59</v>
+        <v>48.6</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|12</t>
+          <t>9|19|20|30|43|3</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
         <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="N9" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1265,19 +1265,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>48.31727272727273</v>
+        <v>47.6</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11|13|20|28|39|18</t>
+          <t>15|20|24|29|39|11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="N10" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>47.59</v>
+        <v>46.35</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>9|22|24|27|29|16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N11" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>46.87571428571429</v>
+        <v>45.32727272727273</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13|15|20|29|30|2</t>
+          <t>7|19|24|34|37|16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -631,7 +631,7 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.6</v>
+        <v>57.58</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.6</v>
+        <v>55.58</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -813,7 +813,7 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>53.1</v>
+        <v>51.58</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -850,28 +850,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -889,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -901,19 +901,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>49.88571428571429</v>
+        <v>50.08</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1|13|18|34|37|5</t>
+          <t>15|20|24|29|39|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -941,28 +941,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -980,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -995,16 +995,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>48.93333333333333</v>
+        <v>49.86571428571428</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3|15|20|29|38|14</t>
+          <t>1|13|18|34|37|5</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
         <v>19</v>
@@ -1044,16 +1044,16 @@
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L7" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1071,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1083,19 +1083,19 @@
         <v>0.5</v>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.6</v>
+        <v>48.91333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>9|19|24|34|41|19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1126,22 +1126,22 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1177,16 +1177,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.6</v>
+        <v>48.58</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9|19|20|30|43|3</t>
+          <t>7|13|25|34|42|11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1217,25 +1217,25 @@
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1268,16 +1268,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>47.6</v>
+        <v>47.58</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15|20|24|29|39|11</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1308,25 +1308,25 @@
         <v>7</v>
       </c>
       <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
         <v>9</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>22</v>
       </c>
-      <c r="J10" t="n">
-        <v>24</v>
-      </c>
       <c r="K10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N10" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.35</v>
+        <v>46.33</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9|22|24|27|29|16</t>
+          <t>8|9|22|29|35|13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1399,25 +1399,25 @@
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="M11" t="n">
         <v>16</v>
       </c>
       <c r="N11" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.32727272727273</v>
+        <v>45.30727272727272</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|16</t>
+          <t>9|22|24|27|29|16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -631,7 +631,7 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.58</v>
+        <v>57.59</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -671,10 +671,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
@@ -683,13 +683,13 @@
         <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="N3" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -719,19 +719,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.58</v>
+        <v>52.59</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|7</t>
+          <t>15|19|24|29|42|18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -762,25 +762,25 @@
         <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -813,16 +813,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.58</v>
+        <v>51.59</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3|21|22|29|38|4</t>
+          <t>11|16|20|31|41|5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -853,25 +853,25 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
         <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -904,16 +904,16 @@
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.08</v>
+        <v>50.09</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15|20|24|29|39|11</t>
+          <t>16|19|22|29|43|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -941,28 +941,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" t="n">
         <v>13</v>
       </c>
-      <c r="J6" t="n">
-        <v>18</v>
-      </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
         <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -995,16 +995,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.86571428571428</v>
+        <v>49.34</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|13|18|34|37|5</t>
+          <t>1|12|13|28|37|18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1035,25 +1035,25 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
         <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1086,16 +1086,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.91333333333333</v>
+        <v>48.92333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9|19|24|34|41|19</t>
+          <t>10|20|23|31|41|15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1129,19 +1129,19 @@
         <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
         <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1177,16 +1177,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.58</v>
+        <v>48.59</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|13|25|34|42|11</t>
+          <t>7|19|24|34|37|12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1265,19 +1265,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>47.58</v>
+        <v>48.31727272727273</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.125</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.33</v>
+        <v>47.59</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8|9|22|29|35|13</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.30727272727272</v>
+        <v>46.87571428571429</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9|22|24|27|29|16</t>
+          <t>13|15|20|29|30|2</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -631,7 +631,7 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.59</v>
+        <v>57.58</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -671,10 +671,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
         <v>15</v>
-      </c>
-      <c r="I3" t="n">
-        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
@@ -683,13 +683,13 @@
         <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -719,19 +719,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>52.59</v>
+        <v>55.58</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15|19|24|29|42|18</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -762,25 +762,25 @@
         <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -813,16 +813,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.59</v>
+        <v>51.58</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11|16|20|31|41|5</t>
+          <t>3|21|22|29|38|4</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -853,25 +853,25 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
         <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -904,16 +904,16 @@
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.09</v>
+        <v>50.08</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16|19|22|29|43|11</t>
+          <t>15|20|24|29|39|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -941,28 +941,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
         <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -995,16 +995,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.34</v>
+        <v>49.86571428571428</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|12|13|28|37|18</t>
+          <t>1|13|18|34|37|5</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1035,25 +1035,25 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L7" t="n">
         <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1086,16 +1086,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.92333333333333</v>
+        <v>48.91333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10|20|23|31|41|15</t>
+          <t>9|19|24|34|41|19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1129,19 +1129,19 @@
         <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
         <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1177,16 +1177,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.59</v>
+        <v>48.58</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|12</t>
+          <t>7|13|25|34|42|11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1265,19 +1265,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>48.31727272727273</v>
+        <v>47.58</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11|13|20|28|39|18</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N10" t="n">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>47.59</v>
+        <v>46.33</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>8|9|22|29|35|13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
+        <v>27</v>
+      </c>
+      <c r="L11" t="n">
         <v>29</v>
       </c>
-      <c r="L11" t="n">
-        <v>30</v>
-      </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N11" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>46.87571428571429</v>
+        <v>45.30727272727272</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13|15|20|29|30|2</t>
+          <t>9|22|24|27|29|16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -580,10 +580,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J2" t="n">
         <v>24</v>
@@ -592,10 +592,10 @@
         <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
         <v>107</v>
@@ -631,16 +631,16 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.58</v>
+        <v>57.57</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7|13|24|29|34|11</t>
+          <t>4|19|24|29|31|10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -671,25 +671,25 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -722,16 +722,16 @@
         <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.58</v>
+        <v>55.57</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|7</t>
+          <t>1|7|21|30|34|2</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -759,28 +759,28 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N4" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -813,16 +813,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.58</v>
+        <v>53.07</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3|21|22|29|38|4</t>
+          <t>1|20|24|41|43|13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="n">
         <v>15</v>
-      </c>
-      <c r="I5" t="n">
-        <v>20</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
@@ -865,13 +865,13 @@
         <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -889,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -901,19 +901,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.08</v>
+        <v>51.57</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15|20|24|29|39|11</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -944,25 +944,25 @@
         <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -995,16 +995,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.86571428571428</v>
+        <v>49.85571428571428</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|13|18|34|37|5</t>
+          <t>9|11|20|41|42|3</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1038,19 +1038,19 @@
         <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
         <v>127</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1086,16 +1086,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.91333333333333</v>
+        <v>48.90333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9|19|24|34|41|19</t>
+          <t>9|14|22|39|43|11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1123,28 +1123,28 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K8" t="n">
+        <v>29</v>
+      </c>
+      <c r="L8" t="n">
         <v>34</v>
       </c>
-      <c r="L8" t="n">
-        <v>42</v>
-      </c>
       <c r="M8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N8" t="n">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
@@ -1177,16 +1177,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.58</v>
+        <v>48.29727272727273</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|13|25|34|42|11</t>
+          <t>1|11|16|29|34|6</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1217,25 +1217,25 @@
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
+        <v>16</v>
+      </c>
+      <c r="J9" t="n">
         <v>19</v>
       </c>
-      <c r="J9" t="n">
-        <v>24</v>
-      </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1268,16 +1268,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>47.58</v>
+        <v>47.57</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>9|16|19|29|34|2</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1308,10 +1308,10 @@
         <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>22</v>
@@ -1320,13 +1320,13 @@
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.33</v>
+        <v>46.32</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8|9|22|29|35|13</t>
+          <t>14|19|22|29|43|4</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1435,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.30727272727272</v>
+        <v>45.57</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9|22|24|27|29|16</t>
+          <t>11|19|24|28|31|3</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -580,25 +580,25 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L2" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="N2" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -607,7 +607,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -628,19 +628,19 @@
         <v>0.5</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.57</v>
+        <v>60.51</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4|19|24|29|31|10</t>
+          <t>9|15|20|38|43|18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -674,22 +674,22 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="L3" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -722,16 +722,16 @@
         <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.57</v>
+        <v>55.51</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1|7|21|30|34|2</t>
+          <t>1|20|24|41|43|13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -759,28 +759,28 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
         <v>43</v>
       </c>
       <c r="M4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -813,16 +813,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>53.07</v>
+        <v>51.51</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1|20|24|41|43|13</t>
+          <t>8|15|24|29|43|6</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="n">
-        <v>8</v>
-      </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
@@ -865,13 +865,13 @@
         <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -889,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -901,19 +901,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>51.57</v>
+        <v>50.01</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|7</t>
+          <t>4|19|24|29|31|10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -941,28 +941,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -980,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -995,16 +995,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.85571428571428</v>
+        <v>49.26</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9|11|20|41|42|3</t>
+          <t>1|13|18|34|37|5</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
         <v>9</v>
@@ -1071,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1086,7 +1086,7 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.90333333333333</v>
+        <v>48.23727272727272</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J8" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K8" t="n">
         <v>29</v>
@@ -1141,10 +1141,10 @@
         <v>34</v>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="N8" t="n">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
@@ -1174,19 +1174,19 @@
         <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.29727272727273</v>
+        <v>47.51</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1|11|16|29|34|6</t>
+          <t>19|21|22|29|34|18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1268,16 +1268,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>47.57</v>
+        <v>46.79571428571428</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9|16|19|29|34|2</t>
+          <t>9|19|24|34|41|18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
         <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N10" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.32</v>
+        <v>45.84333333333333</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14|19|22|29|43|4</t>
+          <t>11|19|24|31|34|11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1399,25 +1399,25 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
         <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.57</v>
+        <v>45.51</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11|19|24|28|31|3</t>
+          <t>14|19|22|29|43|4</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -580,25 +580,25 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K2" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -607,7 +607,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -628,19 +628,19 @@
         <v>0.5</v>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>60.51</v>
+        <v>57.59</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9|15|20|38|43|18</t>
+          <t>7|13|24|29|34|11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -671,22 +671,22 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N3" t="n">
         <v>129</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -719,19 +719,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.51</v>
+        <v>52.59</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1|20|24|41|43|13</t>
+          <t>15|19|24|29|42|18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -762,22 +762,22 @@
         <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
         <v>119</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -813,16 +813,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.51</v>
+        <v>51.59</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|6</t>
+          <t>11|16|20|31|41|5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -853,25 +853,25 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
         <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
         <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -904,16 +904,16 @@
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.01</v>
+        <v>50.09</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4|19|24|29|31|10</t>
+          <t>16|19|22|29|43|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -947,22 +947,22 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" t="n">
         <v>13</v>
       </c>
-      <c r="J6" t="n">
-        <v>18</v>
-      </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
         <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -995,16 +995,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.26</v>
+        <v>49.34</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|13|18|34|37|5</t>
+          <t>1|12|13|28|37|18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1032,28 +1032,28 @@
         </is>
       </c>
       <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
         <v>10</v>
       </c>
-      <c r="H7" t="n">
-        <v>9</v>
-      </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1071,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1086,16 +1086,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.23727272727272</v>
+        <v>48.92333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9|14|22|39|43|11</t>
+          <t>10|20|23|31|41|15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1123,28 +1123,28 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
         <v>19</v>
       </c>
-      <c r="I8" t="n">
-        <v>21</v>
-      </c>
       <c r="J8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
@@ -1174,19 +1174,19 @@
         <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>47.51</v>
+        <v>48.59</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19|21|22|29|34|18</t>
+          <t>7|19|24|34|37|12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
         <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1265,19 +1265,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>46.79571428571428</v>
+        <v>48.31727272727273</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9|19|24|34|41|18</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
         <v>19</v>
@@ -1317,16 +1317,16 @@
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>45.84333333333333</v>
+        <v>47.59</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11|19|24|31|34|11</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
         <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.51</v>
+        <v>46.87571428571429</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14|19|22|29|43|4</t>
+          <t>13|15|20|29|30|2</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -580,25 +580,25 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L2" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N2" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -607,7 +607,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -628,19 +628,19 @@
         <v>0.5</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.59</v>
+        <v>60.63</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7|13|24|29|34|11</t>
+          <t>9|15|20|38|43|18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -668,25 +668,25 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N3" t="n">
         <v>129</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="U3" t="n">
         <v>0.5</v>
@@ -719,19 +719,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>52.59</v>
+        <v>53.13</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15|19|24|29|42|18</t>
+          <t>1|20|24|41|43|13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -759,28 +759,28 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K4" t="n">
+        <v>29</v>
+      </c>
+      <c r="L4" t="n">
+        <v>34</v>
+      </c>
+      <c r="M4" t="n">
         <v>11</v>
       </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K4" t="n">
-        <v>31</v>
-      </c>
-      <c r="L4" t="n">
-        <v>41</v>
-      </c>
-      <c r="M4" t="n">
-        <v>5</v>
-      </c>
       <c r="N4" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -810,19 +810,19 @@
         <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.59</v>
+        <v>52.63</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11|16|20|31|41|5</t>
+          <t>7|13|24|29|34|11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -850,16 +850,16 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
         <v>29</v>
@@ -868,10 +868,10 @@
         <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -889,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -901,19 +901,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.09</v>
+        <v>50.63</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16|19|22|29|43|11</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -944,25 +944,25 @@
         <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M6" t="n">
         <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -995,16 +995,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.34</v>
+        <v>49.38</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|12|13|28|37|18</t>
+          <t>9|19|24|34|41|18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1035,25 +1035,25 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1086,16 +1086,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.92333333333333</v>
+        <v>48.96333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10|20|23|31|41|15</t>
+          <t>14|19|22|29|43|4</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>19</v>
@@ -1135,16 +1135,16 @@
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L8" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
@@ -1174,19 +1174,19 @@
         <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.59</v>
+        <v>48.63</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|12</t>
+          <t>4|19|24|29|31|10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1217,25 +1217,25 @@
         <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1268,16 +1268,16 @@
         <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>48.31727272727273</v>
+        <v>48.35727272727273</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11|13|20|28|39|18</t>
+          <t>5|16|19|29|34|2</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N10" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>47.59</v>
+        <v>46.91571428571429</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>19|21|22|29|34|18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
+        <v>27</v>
+      </c>
+      <c r="L11" t="n">
         <v>29</v>
       </c>
-      <c r="L11" t="n">
-        <v>30</v>
-      </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N11" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>46.87571428571429</v>
+        <v>45.63</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13|15|20|29|30|2</t>
+          <t>9|22|24|27|29|16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -631,7 +631,7 @@
         <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>60.63</v>
+        <v>60.58</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
     </row>
@@ -668,28 +668,28 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U3" t="n">
         <v>0.5</v>
@@ -719,19 +719,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>53.13</v>
+        <v>52.58</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1|20|24|41|43|13</t>
+          <t>7|13|24|29|34|11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
     </row>
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
@@ -774,13 +774,13 @@
         <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -810,19 +810,19 @@
         <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>52.63</v>
+        <v>51.58</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7|13|24|29|34|11</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
     </row>
@@ -853,25 +853,25 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="N5" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -904,16 +904,16 @@
         <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.63</v>
+        <v>50.58</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|7</t>
+          <t>9|19|24|34|41|18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
     </row>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>19</v>
@@ -953,16 +953,16 @@
         <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L6" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -980,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -992,19 +992,19 @@
         <v>0.5</v>
       </c>
       <c r="X6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.38</v>
+        <v>50.08</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9|19|24|34|41|18</t>
+          <t>4|19|24|29|31|10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
     </row>
@@ -1035,22 +1035,22 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" t="n">
         <v>14</v>
-      </c>
-      <c r="I7" t="n">
-        <v>19</v>
       </c>
       <c r="J7" t="n">
         <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L7" t="n">
         <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
         <v>127</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1086,16 +1086,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.96333333333333</v>
+        <v>48.91333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14|19|22|29|43|4</t>
+          <t>9|14|22|39|43|11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
     </row>
@@ -1123,28 +1123,28 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N8" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
@@ -1174,19 +1174,19 @@
         <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.63</v>
+        <v>48.58</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4|19|24|29|31|10</t>
+          <t>7|13|25|34|42|11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
     </row>
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
         <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1265,19 +1265,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>48.35727272727273</v>
+        <v>46.86571428571428</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5|16|19|29|34|2</t>
+          <t>14|19|22|29|43|4</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
     </row>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
+        <v>27</v>
+      </c>
+      <c r="L10" t="n">
         <v>29</v>
       </c>
-      <c r="L10" t="n">
-        <v>34</v>
-      </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N10" t="n">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.91571428571429</v>
+        <v>46.33</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19|21|22|29|34|18</t>
+          <t>9|22|24|27|29|16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
     </row>
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N11" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.63</v>
+        <v>45.30727272727272</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9|22|24|27|29|16</t>
+          <t>3|12|15|29|32|15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -628,10 +628,10 @@
         <v>0.5</v>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>60.58</v>
+        <v>57.6</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -668,28 +668,28 @@
         </is>
       </c>
       <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>7</v>
-      </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="U3" t="n">
         <v>0.5</v>
@@ -719,19 +719,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>52.58</v>
+        <v>53.1</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7|13|24|29|34|11</t>
+          <t>2|22|23|31|43|17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -759,28 +759,28 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L4" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -810,19 +810,19 @@
         <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.58</v>
+        <v>52.6</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|7</t>
+          <t>13|19|24|34|37|3</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -853,25 +853,25 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -904,16 +904,16 @@
         <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.58</v>
+        <v>50.6</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9|19|24|34|41|18</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -941,28 +941,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -980,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -992,19 +992,19 @@
         <v>0.5</v>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>50.08</v>
+        <v>49.35</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4|19|24|29|31|10</t>
+          <t>1|13|18|34|37|5</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1035,25 +1035,25 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N7" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1086,16 +1086,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.91333333333333</v>
+        <v>48.93333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9|14|22|39|43|11</t>
+          <t>3|15|20|29|38|13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1126,19 +1126,19 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
         <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M8" t="n">
         <v>11</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1177,16 +1177,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.58</v>
+        <v>48.6</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|13|25|34|42|11</t>
+          <t>2|20|25|31|43|11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
         <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1268,16 +1268,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>46.86571428571428</v>
+        <v>48.6</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14|19|22|29|43|4</t>
+          <t>4|19|24|29|31|10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L10" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N10" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.33</v>
+        <v>46.88571428571429</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9|22|24|27|29|16</t>
+          <t>9|19|24|34|41|18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1399,25 +1399,25 @@
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L11" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N11" t="n">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.30727272727272</v>
+        <v>45.32727272727273</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3|12|15|29|32|15</t>
+          <t>9|14|22|39|43|11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -580,25 +580,25 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K2" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -607,7 +607,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -631,16 +631,16 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.6</v>
+        <v>57.59</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9|15|20|38|43|18</t>
+          <t>7|13|24|29|34|11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -668,28 +668,28 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N3" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U3" t="n">
         <v>0.5</v>
@@ -719,19 +719,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>53.1</v>
+        <v>52.59</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2|22|23|31|43|17</t>
+          <t>15|19|24|29|42|18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -759,28 +759,28 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -810,19 +810,19 @@
         <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>52.6</v>
+        <v>51.59</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13|19|24|34|37|3</t>
+          <t>11|16|20|31|41|5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -850,16 +850,16 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
         <v>29</v>
@@ -868,10 +868,10 @@
         <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -889,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -901,19 +901,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.6</v>
+        <v>50.09</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|7</t>
+          <t>16|19|22|29|43|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -947,22 +947,22 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" t="n">
         <v>13</v>
       </c>
-      <c r="J6" t="n">
-        <v>18</v>
-      </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
         <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -995,16 +995,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.35</v>
+        <v>49.34</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|13|18|34|37|5</t>
+          <t>1|12|13|28|37|18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1035,25 +1035,25 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>23</v>
+      </c>
+      <c r="K7" t="n">
+        <v>31</v>
+      </c>
+      <c r="L7" t="n">
+        <v>41</v>
+      </c>
+      <c r="M7" t="n">
         <v>15</v>
       </c>
-      <c r="J7" t="n">
-        <v>20</v>
-      </c>
-      <c r="K7" t="n">
-        <v>29</v>
-      </c>
-      <c r="L7" t="n">
-        <v>38</v>
-      </c>
-      <c r="M7" t="n">
-        <v>13</v>
-      </c>
       <c r="N7" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1086,16 +1086,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.93333333333333</v>
+        <v>48.92333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3|15|20|29|38|13</t>
+          <t>10|20|23|31|41|15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1126,22 +1126,22 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1177,16 +1177,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.6</v>
+        <v>48.59</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2|20|25|31|43|11</t>
+          <t>7|19|24|34|37|12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1265,19 +1265,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>48.6</v>
+        <v>48.31727272727273</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4|19|24|29|31|10</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
         <v>19</v>
@@ -1317,16 +1317,16 @@
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.88571428571429</v>
+        <v>47.59</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9|19|24|34|41|18</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.32727272727273</v>
+        <v>46.87571428571429</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9|14|22|39|43|11</t>
+          <t>13|15|20|29|30|2</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -580,25 +580,25 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L2" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N2" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -607,7 +607,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -628,19 +628,19 @@
         <v>0.5</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.59</v>
+        <v>60.62</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7|13|24|29|34|11</t>
+          <t>2|22|23|31|43|17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
         <v>15</v>
-      </c>
-      <c r="I3" t="n">
-        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
@@ -683,13 +683,13 @@
         <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="U3" t="n">
         <v>0.5</v>
@@ -719,19 +719,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>52.59</v>
+        <v>53.12</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15|19|24|29|42|18</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -759,28 +759,28 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
         <v>4</v>
       </c>
-      <c r="H4" t="n">
-        <v>11</v>
-      </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
+        <v>29</v>
+      </c>
+      <c r="L4" t="n">
         <v>31</v>
       </c>
-      <c r="L4" t="n">
-        <v>41</v>
-      </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -810,19 +810,19 @@
         <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.59</v>
+        <v>52.62</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11|16|20|31|41|5</t>
+          <t>4|19|24|29|31|10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -850,28 +850,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" t="n">
         <v>16</v>
       </c>
-      <c r="I5" t="n">
-        <v>19</v>
-      </c>
-      <c r="J5" t="n">
-        <v>22</v>
-      </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
         <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -889,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -901,19 +901,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.09</v>
+        <v>50.62</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16|19|22|29|43|11</t>
+          <t>9|15|16|32|43|2</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -941,28 +941,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -980,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -995,16 +995,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.34</v>
+        <v>48.95333333333333</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|12|13|28|37|18</t>
+          <t>3|19|24|27|40|15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1032,28 +1032,28 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L7" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1071,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1083,19 +1083,19 @@
         <v>0.5</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.92333333333333</v>
+        <v>48.62</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10|20|23|31|41|15</t>
+          <t>7|19|24|34|37|16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1126,25 +1126,25 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L8" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N8" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1177,16 +1177,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.59</v>
+        <v>48.62</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|12</t>
+          <t>1|12|24|29|41|15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1265,19 +1265,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>48.31727272727273</v>
+        <v>46.90571428571428</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11|13|20|28|39|18</t>
+          <t>9|15|19|30|34|2</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="N10" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1359,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>47.59</v>
+        <v>46.37</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>15|20|22|33|35|16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
         <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N11" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1450,16 +1450,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>46.87571428571429</v>
+        <v>45.34727272727272</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13|15|20|29|30|2</t>
+          <t>13|19|24|35|36|13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/powerball_ensemble_predictions.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
